--- a/1_metafiles/design_AS_soil.xlsx
+++ b/1_metafiles/design_AS_soil.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/j.waechli/Desktop/Jan_Waelchli/01_Projects/01_Support/Vero/01_ASV_Arsen_trt/reanalysis_BE05_BE08/06_ENA upload/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3687FE-EC53-7C48-A19F-43D49171A88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="653">
   <si>
     <t>SampleID</t>
   </si>
@@ -1433,124 +1441,555 @@
     <t>FLD0334</t>
   </si>
   <si>
-    <t>soil_bacteria_0ppm_0M</t>
-  </si>
-  <si>
-    <t>soil_fungi_0ppm_0M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_100ppm_0M</t>
-  </si>
-  <si>
-    <t>soil_fungi_100ppm_0M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_200ppm_0M</t>
-  </si>
-  <si>
-    <t>soil_fungi_200ppm_0M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_0ppm_1M</t>
-  </si>
-  <si>
-    <t>soil_fungi_0ppm_1M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_100ppm_1M</t>
-  </si>
-  <si>
-    <t>soil_fungi_100ppm_1M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_200ppm_1M</t>
-  </si>
-  <si>
-    <t>soil_fungi_200ppm_1M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_0ppm_2M</t>
-  </si>
-  <si>
-    <t>soil_fungi_0ppm_2M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_100ppm_2M</t>
-  </si>
-  <si>
-    <t>soil_fungi_100ppm_2M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_200ppm_2M</t>
-  </si>
-  <si>
-    <t>soil_fungi_200ppm_2M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_0ppm_3M</t>
-  </si>
-  <si>
-    <t>soil_fungi_0ppm_3M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_100ppm_3M</t>
-  </si>
-  <si>
-    <t>soil_fungi_100ppm_3M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_200ppm_3M</t>
-  </si>
-  <si>
-    <t>soil_fungi_200ppm_3M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_0ppm_4M</t>
-  </si>
-  <si>
-    <t>soil_fungi_0ppm_4M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_100ppm_4M</t>
-  </si>
-  <si>
-    <t>soil_fungi_100ppm_4M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_200ppm_4M</t>
-  </si>
-  <si>
-    <t>soil_fungi_200ppm_4M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_0ppm_5M</t>
-  </si>
-  <si>
-    <t>soil_fungi_0ppm_5M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_100ppm_5M</t>
-  </si>
-  <si>
-    <t>soil_fungi_100ppm_5M</t>
-  </si>
-  <si>
-    <t>soil_bacteria_200ppm_5M</t>
-  </si>
-  <si>
-    <t>soil_fungi_200ppm_5M</t>
+    <t>soil_bacteria_0ppm_0M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_0M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_0M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_0M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_0M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_0M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_0M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_0M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_0M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_0M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_0M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_0M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_0M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_0M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_0M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_0M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_0M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_0M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_0M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_0M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_0M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_0M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_0M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_0M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_0M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_0M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_0M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_0M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_0M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_0M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_1M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_1M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_1M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_1M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_1M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_1M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_1M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_1M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_1M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_1M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_1M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_1M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_1M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_1M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_1M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_1M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_1M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_1M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_1M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_1M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_1M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_1M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_1M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_1M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_1M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_1M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_1M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_1M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_1M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_1M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_2M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_2M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_2M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_2M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_2M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_2M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_2M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_2M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_2M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_2M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_2M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_2M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_2M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_2M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_2M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_2M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_2M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_2M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_2M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_2M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_2M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_2M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_2M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_2M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_2M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_2M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_2M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_2M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_2M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_2M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_3M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_3M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_3M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_3M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_3M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_3M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_3M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_3M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_3M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_3M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_3M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_3M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_3M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_3M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_3M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_3M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_3M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_3M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_3M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_3M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_3M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_3M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_3M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_3M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_3M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_3M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_3M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_3M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_3M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_3M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_4M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_4M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_4M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_4M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_4M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_4M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_4M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_4M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_4M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_4M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_4M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_4M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_4M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_4M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_4M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_4M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_4M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_4M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_4M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_4M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_4M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_4M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_4M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_4M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_4M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_4M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_4M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_4M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_4M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_4M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_5M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_5M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_5M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_5M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_5M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_5M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_5M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_5M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_0ppm_5M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_0ppm_5M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_5M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_5M_1</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_5M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_5M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_5M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_5M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_5M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_5M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_100ppm_5M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_100ppm_5M_5</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_5M_1</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_5M_0</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_5M_2</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_5M_2</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_5M_3</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_5M_3</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_5M_4</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_5M_4</t>
+  </si>
+  <si>
+    <t>soil_bacteria_200ppm_5M_5</t>
+  </si>
+  <si>
+    <t>soil_fungi_200ppm_5M_5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1560,7 +1999,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -1578,16 +2017,343 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J181"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1"/>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1616,7 +2382,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1648,7 +2414,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1680,7 +2446,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1709,10 +2475,10 @@
         <v>295</v>
       </c>
       <c r="J4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1741,10 +2507,10 @@
         <v>296</v>
       </c>
       <c r="J5" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1773,10 +2539,10 @@
         <v>297</v>
       </c>
       <c r="J6" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1805,10 +2571,10 @@
         <v>298</v>
       </c>
       <c r="J7" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1837,10 +2603,10 @@
         <v>299</v>
       </c>
       <c r="J8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1869,10 +2635,10 @@
         <v>300</v>
       </c>
       <c r="J9" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1901,10 +2667,10 @@
         <v>301</v>
       </c>
       <c r="J10" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1933,10 +2699,10 @@
         <v>302</v>
       </c>
       <c r="J11" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1965,10 +2731,10 @@
         <v>303</v>
       </c>
       <c r="J12" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1997,10 +2763,10 @@
         <v>304</v>
       </c>
       <c r="J13" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2029,10 +2795,10 @@
         <v>305</v>
       </c>
       <c r="J14" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -2061,10 +2827,10 @@
         <v>306</v>
       </c>
       <c r="J15" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -2093,10 +2859,10 @@
         <v>307</v>
       </c>
       <c r="J16" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -2125,10 +2891,10 @@
         <v>308</v>
       </c>
       <c r="J17" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -2157,10 +2923,10 @@
         <v>309</v>
       </c>
       <c r="J18" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -2189,10 +2955,10 @@
         <v>310</v>
       </c>
       <c r="J19" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -2221,10 +2987,10 @@
         <v>311</v>
       </c>
       <c r="J20" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2253,10 +3019,10 @@
         <v>312</v>
       </c>
       <c r="J21" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -2285,10 +3051,10 @@
         <v>313</v>
       </c>
       <c r="J22" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -2317,10 +3083,10 @@
         <v>314</v>
       </c>
       <c r="J23" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -2349,10 +3115,10 @@
         <v>315</v>
       </c>
       <c r="J24" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2381,10 +3147,10 @@
         <v>316</v>
       </c>
       <c r="J25" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -2413,10 +3179,10 @@
         <v>317</v>
       </c>
       <c r="J26" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -2445,10 +3211,10 @@
         <v>318</v>
       </c>
       <c r="J27" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -2477,10 +3243,10 @@
         <v>319</v>
       </c>
       <c r="J28" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -2509,10 +3275,10 @@
         <v>320</v>
       </c>
       <c r="J29" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -2541,10 +3307,10 @@
         <v>321</v>
       </c>
       <c r="J30" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -2573,10 +3339,10 @@
         <v>322</v>
       </c>
       <c r="J31" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -2605,10 +3371,10 @@
         <v>323</v>
       </c>
       <c r="J32" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -2637,10 +3403,10 @@
         <v>324</v>
       </c>
       <c r="J33" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -2669,10 +3435,10 @@
         <v>325</v>
       </c>
       <c r="J34" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -2701,10 +3467,10 @@
         <v>326</v>
       </c>
       <c r="J35" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -2733,10 +3499,10 @@
         <v>327</v>
       </c>
       <c r="J36" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -2765,10 +3531,10 @@
         <v>328</v>
       </c>
       <c r="J37" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -2797,10 +3563,10 @@
         <v>329</v>
       </c>
       <c r="J38" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -2829,10 +3595,10 @@
         <v>330</v>
       </c>
       <c r="J39" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -2861,10 +3627,10 @@
         <v>331</v>
       </c>
       <c r="J40" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -2893,10 +3659,10 @@
         <v>332</v>
       </c>
       <c r="J41" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -2925,10 +3691,10 @@
         <v>333</v>
       </c>
       <c r="J42" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -2957,10 +3723,10 @@
         <v>334</v>
       </c>
       <c r="J43" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -2989,10 +3755,10 @@
         <v>335</v>
       </c>
       <c r="J44" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -3021,10 +3787,10 @@
         <v>336</v>
       </c>
       <c r="J45" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -3053,10 +3819,10 @@
         <v>337</v>
       </c>
       <c r="J46" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -3085,10 +3851,10 @@
         <v>338</v>
       </c>
       <c r="J47" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -3117,10 +3883,10 @@
         <v>339</v>
       </c>
       <c r="J48" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -3149,10 +3915,10 @@
         <v>340</v>
       </c>
       <c r="J49" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -3181,10 +3947,10 @@
         <v>341</v>
       </c>
       <c r="J50" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -3213,10 +3979,10 @@
         <v>342</v>
       </c>
       <c r="J51" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -3245,10 +4011,10 @@
         <v>343</v>
       </c>
       <c r="J52" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -3277,10 +4043,10 @@
         <v>344</v>
       </c>
       <c r="J53" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -3309,10 +4075,10 @@
         <v>345</v>
       </c>
       <c r="J54" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -3341,10 +4107,10 @@
         <v>346</v>
       </c>
       <c r="J55" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -3373,10 +4139,10 @@
         <v>347</v>
       </c>
       <c r="J56" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -3405,10 +4171,10 @@
         <v>348</v>
       </c>
       <c r="J57" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -3437,10 +4203,10 @@
         <v>349</v>
       </c>
       <c r="J58" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -3469,10 +4235,10 @@
         <v>350</v>
       </c>
       <c r="J59" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -3501,10 +4267,10 @@
         <v>351</v>
       </c>
       <c r="J60" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -3533,10 +4299,10 @@
         <v>352</v>
       </c>
       <c r="J61" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -3565,10 +4331,10 @@
         <v>353</v>
       </c>
       <c r="J62" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -3597,10 +4363,10 @@
         <v>354</v>
       </c>
       <c r="J63" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>71</v>
       </c>
@@ -3629,10 +4395,10 @@
         <v>355</v>
       </c>
       <c r="J64" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>72</v>
       </c>
@@ -3661,10 +4427,10 @@
         <v>356</v>
       </c>
       <c r="J65" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>73</v>
       </c>
@@ -3693,10 +4459,10 @@
         <v>357</v>
       </c>
       <c r="J66" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -3725,10 +4491,10 @@
         <v>358</v>
       </c>
       <c r="J67" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -3757,10 +4523,10 @@
         <v>359</v>
       </c>
       <c r="J68" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>76</v>
       </c>
@@ -3789,10 +4555,10 @@
         <v>360</v>
       </c>
       <c r="J69" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -3821,10 +4587,10 @@
         <v>361</v>
       </c>
       <c r="J70" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>78</v>
       </c>
@@ -3853,10 +4619,10 @@
         <v>362</v>
       </c>
       <c r="J71" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -3885,10 +4651,10 @@
         <v>363</v>
       </c>
       <c r="J72" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>80</v>
       </c>
@@ -3917,10 +4683,10 @@
         <v>364</v>
       </c>
       <c r="J73" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -3949,10 +4715,10 @@
         <v>365</v>
       </c>
       <c r="J74" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -3981,10 +4747,10 @@
         <v>366</v>
       </c>
       <c r="J75" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -4013,10 +4779,10 @@
         <v>367</v>
       </c>
       <c r="J76" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>84</v>
       </c>
@@ -4045,10 +4811,10 @@
         <v>368</v>
       </c>
       <c r="J77" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>85</v>
       </c>
@@ -4077,10 +4843,10 @@
         <v>369</v>
       </c>
       <c r="J78" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>86</v>
       </c>
@@ -4109,10 +4875,10 @@
         <v>370</v>
       </c>
       <c r="J79" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>87</v>
       </c>
@@ -4141,10 +4907,10 @@
         <v>371</v>
       </c>
       <c r="J80" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>88</v>
       </c>
@@ -4173,10 +4939,10 @@
         <v>372</v>
       </c>
       <c r="J81" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>89</v>
       </c>
@@ -4205,10 +4971,10 @@
         <v>373</v>
       </c>
       <c r="J82" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>90</v>
       </c>
@@ -4237,10 +5003,10 @@
         <v>374</v>
       </c>
       <c r="J83" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>91</v>
       </c>
@@ -4269,10 +5035,10 @@
         <v>375</v>
       </c>
       <c r="J84" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>92</v>
       </c>
@@ -4301,10 +5067,10 @@
         <v>376</v>
       </c>
       <c r="J85" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>93</v>
       </c>
@@ -4333,10 +5099,10 @@
         <v>377</v>
       </c>
       <c r="J86" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>94</v>
       </c>
@@ -4365,10 +5131,10 @@
         <v>378</v>
       </c>
       <c r="J87" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>95</v>
       </c>
@@ -4397,10 +5163,10 @@
         <v>379</v>
       </c>
       <c r="J88" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>96</v>
       </c>
@@ -4429,10 +5195,10 @@
         <v>380</v>
       </c>
       <c r="J89" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>97</v>
       </c>
@@ -4461,10 +5227,10 @@
         <v>381</v>
       </c>
       <c r="J90" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>98</v>
       </c>
@@ -4493,10 +5259,10 @@
         <v>382</v>
       </c>
       <c r="J91" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>99</v>
       </c>
@@ -4525,10 +5291,10 @@
         <v>383</v>
       </c>
       <c r="J92" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>100</v>
       </c>
@@ -4557,10 +5323,10 @@
         <v>384</v>
       </c>
       <c r="J93" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>101</v>
       </c>
@@ -4589,10 +5355,10 @@
         <v>385</v>
       </c>
       <c r="J94" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>102</v>
       </c>
@@ -4621,10 +5387,10 @@
         <v>386</v>
       </c>
       <c r="J95" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>103</v>
       </c>
@@ -4653,10 +5419,10 @@
         <v>387</v>
       </c>
       <c r="J96" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>104</v>
       </c>
@@ -4685,10 +5451,10 @@
         <v>388</v>
       </c>
       <c r="J97" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>105</v>
       </c>
@@ -4717,10 +5483,10 @@
         <v>389</v>
       </c>
       <c r="J98" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="99">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>106</v>
       </c>
@@ -4749,10 +5515,10 @@
         <v>390</v>
       </c>
       <c r="J99" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="100">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>107</v>
       </c>
@@ -4781,10 +5547,10 @@
         <v>391</v>
       </c>
       <c r="J100" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="101">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>108</v>
       </c>
@@ -4813,10 +5579,10 @@
         <v>392</v>
       </c>
       <c r="J101" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="102">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>109</v>
       </c>
@@ -4845,10 +5611,10 @@
         <v>393</v>
       </c>
       <c r="J102" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="103">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>110</v>
       </c>
@@ -4877,10 +5643,10 @@
         <v>394</v>
       </c>
       <c r="J103" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="104">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>111</v>
       </c>
@@ -4909,10 +5675,10 @@
         <v>395</v>
       </c>
       <c r="J104" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="105">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>112</v>
       </c>
@@ -4941,10 +5707,10 @@
         <v>396</v>
       </c>
       <c r="J105" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="106">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>113</v>
       </c>
@@ -4973,10 +5739,10 @@
         <v>397</v>
       </c>
       <c r="J106" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="107">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -5005,10 +5771,10 @@
         <v>398</v>
       </c>
       <c r="J107" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="108">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>115</v>
       </c>
@@ -5037,10 +5803,10 @@
         <v>399</v>
       </c>
       <c r="J108" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="109">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>116</v>
       </c>
@@ -5069,10 +5835,10 @@
         <v>400</v>
       </c>
       <c r="J109" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="110">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>117</v>
       </c>
@@ -5101,10 +5867,10 @@
         <v>401</v>
       </c>
       <c r="J110" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="111">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>118</v>
       </c>
@@ -5133,10 +5899,10 @@
         <v>402</v>
       </c>
       <c r="J111" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="112">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>119</v>
       </c>
@@ -5165,10 +5931,10 @@
         <v>403</v>
       </c>
       <c r="J112" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="113">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>120</v>
       </c>
@@ -5197,10 +5963,10 @@
         <v>404</v>
       </c>
       <c r="J113" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="114">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>121</v>
       </c>
@@ -5229,10 +5995,10 @@
         <v>405</v>
       </c>
       <c r="J114" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="115">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>122</v>
       </c>
@@ -5261,10 +6027,10 @@
         <v>406</v>
       </c>
       <c r="J115" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="116">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>123</v>
       </c>
@@ -5293,10 +6059,10 @@
         <v>407</v>
       </c>
       <c r="J116" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="117">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>124</v>
       </c>
@@ -5325,10 +6091,10 @@
         <v>408</v>
       </c>
       <c r="J117" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="118">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>125</v>
       </c>
@@ -5357,10 +6123,10 @@
         <v>409</v>
       </c>
       <c r="J118" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="119">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>126</v>
       </c>
@@ -5389,10 +6155,10 @@
         <v>410</v>
       </c>
       <c r="J119" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="120">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>127</v>
       </c>
@@ -5421,10 +6187,10 @@
         <v>411</v>
       </c>
       <c r="J120" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="121">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>128</v>
       </c>
@@ -5453,10 +6219,10 @@
         <v>412</v>
       </c>
       <c r="J121" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="122">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>129</v>
       </c>
@@ -5485,10 +6251,10 @@
         <v>413</v>
       </c>
       <c r="J122" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="123">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>130</v>
       </c>
@@ -5517,10 +6283,10 @@
         <v>414</v>
       </c>
       <c r="J123" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="124">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>131</v>
       </c>
@@ -5549,10 +6315,10 @@
         <v>415</v>
       </c>
       <c r="J124" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="125">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -5581,10 +6347,10 @@
         <v>416</v>
       </c>
       <c r="J125" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="126">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>133</v>
       </c>
@@ -5613,10 +6379,10 @@
         <v>417</v>
       </c>
       <c r="J126" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="127">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>134</v>
       </c>
@@ -5645,10 +6411,10 @@
         <v>418</v>
       </c>
       <c r="J127" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="128">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>135</v>
       </c>
@@ -5677,10 +6443,10 @@
         <v>419</v>
       </c>
       <c r="J128" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="129">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>136</v>
       </c>
@@ -5709,10 +6475,10 @@
         <v>420</v>
       </c>
       <c r="J129" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="130">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>137</v>
       </c>
@@ -5741,10 +6507,10 @@
         <v>421</v>
       </c>
       <c r="J130" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="131">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>138</v>
       </c>
@@ -5773,10 +6539,10 @@
         <v>422</v>
       </c>
       <c r="J131" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="132">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>139</v>
       </c>
@@ -5805,10 +6571,10 @@
         <v>423</v>
       </c>
       <c r="J132" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="133">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>140</v>
       </c>
@@ -5837,10 +6603,10 @@
         <v>424</v>
       </c>
       <c r="J133" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="134">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>141</v>
       </c>
@@ -5869,10 +6635,10 @@
         <v>425</v>
       </c>
       <c r="J134" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="135">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>142</v>
       </c>
@@ -5901,10 +6667,10 @@
         <v>426</v>
       </c>
       <c r="J135" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="136">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>143</v>
       </c>
@@ -5933,10 +6699,10 @@
         <v>427</v>
       </c>
       <c r="J136" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="137">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>144</v>
       </c>
@@ -5965,10 +6731,10 @@
         <v>428</v>
       </c>
       <c r="J137" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="138">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>145</v>
       </c>
@@ -5997,10 +6763,10 @@
         <v>429</v>
       </c>
       <c r="J138" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="139">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>146</v>
       </c>
@@ -6029,10 +6795,10 @@
         <v>430</v>
       </c>
       <c r="J139" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="140">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>147</v>
       </c>
@@ -6061,10 +6827,10 @@
         <v>431</v>
       </c>
       <c r="J140" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="141">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>148</v>
       </c>
@@ -6093,10 +6859,10 @@
         <v>432</v>
       </c>
       <c r="J141" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="142">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>149</v>
       </c>
@@ -6125,10 +6891,10 @@
         <v>433</v>
       </c>
       <c r="J142" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="143">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>150</v>
       </c>
@@ -6157,10 +6923,10 @@
         <v>434</v>
       </c>
       <c r="J143" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="144">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>151</v>
       </c>
@@ -6189,10 +6955,10 @@
         <v>435</v>
       </c>
       <c r="J144" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="145">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>152</v>
       </c>
@@ -6221,10 +6987,10 @@
         <v>436</v>
       </c>
       <c r="J145" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="146">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>153</v>
       </c>
@@ -6253,10 +7019,10 @@
         <v>437</v>
       </c>
       <c r="J146" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="147">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>154</v>
       </c>
@@ -6285,10 +7051,10 @@
         <v>438</v>
       </c>
       <c r="J147" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="148">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>155</v>
       </c>
@@ -6317,10 +7083,10 @@
         <v>439</v>
       </c>
       <c r="J148" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="149">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>156</v>
       </c>
@@ -6349,10 +7115,10 @@
         <v>440</v>
       </c>
       <c r="J149" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="150">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>157</v>
       </c>
@@ -6381,10 +7147,10 @@
         <v>441</v>
       </c>
       <c r="J150" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="151">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>158</v>
       </c>
@@ -6413,10 +7179,10 @@
         <v>442</v>
       </c>
       <c r="J151" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="152">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>159</v>
       </c>
@@ -6445,10 +7211,10 @@
         <v>443</v>
       </c>
       <c r="J152" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="153">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>160</v>
       </c>
@@ -6477,10 +7243,10 @@
         <v>444</v>
       </c>
       <c r="J153" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="154">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>161</v>
       </c>
@@ -6509,10 +7275,10 @@
         <v>445</v>
       </c>
       <c r="J154" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="155">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>162</v>
       </c>
@@ -6541,10 +7307,10 @@
         <v>446</v>
       </c>
       <c r="J155" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="156">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>163</v>
       </c>
@@ -6573,10 +7339,10 @@
         <v>447</v>
       </c>
       <c r="J156" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="157">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>164</v>
       </c>
@@ -6605,10 +7371,10 @@
         <v>448</v>
       </c>
       <c r="J157" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="158">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>165</v>
       </c>
@@ -6637,10 +7403,10 @@
         <v>449</v>
       </c>
       <c r="J158" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="159">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>166</v>
       </c>
@@ -6669,10 +7435,10 @@
         <v>450</v>
       </c>
       <c r="J159" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="160">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>167</v>
       </c>
@@ -6701,10 +7467,10 @@
         <v>451</v>
       </c>
       <c r="J160" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="161">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>168</v>
       </c>
@@ -6733,10 +7499,10 @@
         <v>452</v>
       </c>
       <c r="J161" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="162">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>169</v>
       </c>
@@ -6765,10 +7531,10 @@
         <v>453</v>
       </c>
       <c r="J162" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="163">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>170</v>
       </c>
@@ -6797,10 +7563,10 @@
         <v>454</v>
       </c>
       <c r="J163" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="164">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>171</v>
       </c>
@@ -6829,10 +7595,10 @@
         <v>455</v>
       </c>
       <c r="J164" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="165">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>172</v>
       </c>
@@ -6861,10 +7627,10 @@
         <v>456</v>
       </c>
       <c r="J165" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="166">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>173</v>
       </c>
@@ -6893,10 +7659,10 @@
         <v>457</v>
       </c>
       <c r="J166" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="167">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>174</v>
       </c>
@@ -6925,10 +7691,10 @@
         <v>458</v>
       </c>
       <c r="J167" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="168">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>175</v>
       </c>
@@ -6957,10 +7723,10 @@
         <v>459</v>
       </c>
       <c r="J168" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="169">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>176</v>
       </c>
@@ -6989,10 +7755,10 @@
         <v>460</v>
       </c>
       <c r="J169" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="170">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>177</v>
       </c>
@@ -7021,10 +7787,10 @@
         <v>461</v>
       </c>
       <c r="J170" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="171">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>178</v>
       </c>
@@ -7053,10 +7819,10 @@
         <v>462</v>
       </c>
       <c r="J171" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="172">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>179</v>
       </c>
@@ -7085,10 +7851,10 @@
         <v>463</v>
       </c>
       <c r="J172" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="173">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>180</v>
       </c>
@@ -7117,10 +7883,10 @@
         <v>464</v>
       </c>
       <c r="J173" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="174">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>181</v>
       </c>
@@ -7149,10 +7915,10 @@
         <v>465</v>
       </c>
       <c r="J174" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="175">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>182</v>
       </c>
@@ -7181,10 +7947,10 @@
         <v>466</v>
       </c>
       <c r="J175" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="176">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>183</v>
       </c>
@@ -7213,10 +7979,10 @@
         <v>467</v>
       </c>
       <c r="J176" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="177">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>184</v>
       </c>
@@ -7245,10 +8011,10 @@
         <v>468</v>
       </c>
       <c r="J177" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="178">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>185</v>
       </c>
@@ -7277,10 +8043,10 @@
         <v>469</v>
       </c>
       <c r="J178" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="179">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>186</v>
       </c>
@@ -7309,10 +8075,10 @@
         <v>470</v>
       </c>
       <c r="J179" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="180">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>187</v>
       </c>
@@ -7341,10 +8107,10 @@
         <v>471</v>
       </c>
       <c r="J180" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="181">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>188</v>
       </c>
@@ -7373,10 +8139,10 @@
         <v>472</v>
       </c>
       <c r="J181" t="s">
-        <v>508</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/1_metafiles/design_AS_soil.xlsx
+++ b/1_metafiles/design_AS_soil.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/j.waechli/Desktop/Jan_Waelchli/01_Projects/01_Support/Vero/01_ASV_Arsen_trt/reanalysis_BE05_BE08/06_ENA upload/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/j.waechli/Desktop/Jan_Waelchli/01_Projects/01_Support/Vero/01_ASV_Arsen_trt/reanalysis_BE05_BE08/05_github/1_metafiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3687FE-EC53-7C48-A19F-43D49171A88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8631F4BD-98F9-604B-82CC-AB79433237EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="647">
   <si>
     <t>SampleID</t>
   </si>
@@ -403,9 +403,6 @@
     <t>118</t>
   </si>
   <si>
-    <t>119</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -457,9 +454,6 @@
     <t>136</t>
   </si>
   <si>
-    <t>137</t>
-  </si>
-  <si>
     <t>138</t>
   </si>
   <si>
@@ -1255,9 +1249,6 @@
     <t>FLD0303</t>
   </si>
   <si>
-    <t>FLD0112</t>
-  </si>
-  <si>
     <t>FLD0304</t>
   </si>
   <si>
@@ -1309,9 +1300,6 @@
     <t>FLD0321</t>
   </si>
   <si>
-    <t>FLD0373</t>
-  </si>
-  <si>
     <t>FLD0322</t>
   </si>
   <si>
@@ -1795,9 +1783,6 @@
     <t>soil_fungi_200ppm_3M_4</t>
   </si>
   <si>
-    <t>soil_bacteria_200ppm_3M_5</t>
-  </si>
-  <si>
     <t>soil_fungi_200ppm_3M_5</t>
   </si>
   <si>
@@ -1847,9 +1832,6 @@
   </si>
   <si>
     <t>soil_fungi_100ppm_4M_3</t>
-  </si>
-  <si>
-    <t>soil_bacteria_100ppm_4M_4</t>
   </si>
   <si>
     <t>soil_fungi_100ppm_4M_4</t>
@@ -2350,7 +2332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J181"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -2387,31 +2369,31 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E2" t="s">
         <v>279</v>
       </c>
-      <c r="D2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E2" t="s">
-        <v>281</v>
-      </c>
       <c r="F2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I2" t="s">
         <v>291</v>
       </c>
-      <c r="I2" t="s">
-        <v>293</v>
-      </c>
       <c r="J2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2419,31 +2401,31 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E3" t="s">
         <v>279</v>
       </c>
-      <c r="D3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E3" t="s">
-        <v>281</v>
-      </c>
       <c r="F3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H3" t="s">
+        <v>290</v>
+      </c>
+      <c r="I3" t="s">
         <v>292</v>
       </c>
-      <c r="I3" t="s">
-        <v>294</v>
-      </c>
       <c r="J3" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2451,31 +2433,31 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E4" t="s">
         <v>279</v>
       </c>
-      <c r="D4" t="s">
-        <v>280</v>
-      </c>
-      <c r="E4" t="s">
-        <v>281</v>
-      </c>
       <c r="F4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J4" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2483,31 +2465,31 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D5" t="s">
+        <v>278</v>
+      </c>
+      <c r="E5" t="s">
         <v>279</v>
       </c>
-      <c r="D5" t="s">
-        <v>280</v>
-      </c>
-      <c r="E5" t="s">
-        <v>281</v>
-      </c>
       <c r="F5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J5" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -2515,31 +2497,31 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E6" t="s">
         <v>279</v>
       </c>
-      <c r="D6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E6" t="s">
-        <v>281</v>
-      </c>
       <c r="F6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J6" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -2547,31 +2529,31 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E7" t="s">
         <v>279</v>
       </c>
-      <c r="D7" t="s">
-        <v>280</v>
-      </c>
-      <c r="E7" t="s">
-        <v>281</v>
-      </c>
       <c r="F7" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H7" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J7" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -2579,31 +2561,31 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
+        <v>277</v>
+      </c>
+      <c r="D8" t="s">
+        <v>278</v>
+      </c>
+      <c r="E8" t="s">
         <v>279</v>
       </c>
-      <c r="D8" t="s">
-        <v>280</v>
-      </c>
-      <c r="E8" t="s">
-        <v>281</v>
-      </c>
       <c r="F8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J8" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -2611,31 +2593,31 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C9" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" t="s">
+        <v>278</v>
+      </c>
+      <c r="E9" t="s">
         <v>279</v>
       </c>
-      <c r="D9" t="s">
-        <v>280</v>
-      </c>
-      <c r="E9" t="s">
-        <v>281</v>
-      </c>
       <c r="F9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J9" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -2643,31 +2625,31 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D10" t="s">
+        <v>278</v>
+      </c>
+      <c r="E10" t="s">
         <v>279</v>
       </c>
-      <c r="D10" t="s">
-        <v>280</v>
-      </c>
-      <c r="E10" t="s">
-        <v>281</v>
-      </c>
       <c r="F10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J10" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -2675,31 +2657,31 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C11" t="s">
+        <v>277</v>
+      </c>
+      <c r="D11" t="s">
+        <v>278</v>
+      </c>
+      <c r="E11" t="s">
         <v>279</v>
       </c>
-      <c r="D11" t="s">
-        <v>280</v>
-      </c>
-      <c r="E11" t="s">
-        <v>281</v>
-      </c>
       <c r="F11" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J11" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -2707,31 +2689,31 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E12" t="s">
         <v>280</v>
       </c>
-      <c r="E12" t="s">
-        <v>282</v>
-      </c>
       <c r="F12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J12" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -2739,31 +2721,31 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D13" t="s">
+        <v>278</v>
+      </c>
+      <c r="E13" t="s">
         <v>280</v>
       </c>
-      <c r="E13" t="s">
-        <v>282</v>
-      </c>
       <c r="F13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G13" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H13" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I13" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J13" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -2771,31 +2753,31 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C14" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D14" t="s">
+        <v>278</v>
+      </c>
+      <c r="E14" t="s">
         <v>280</v>
       </c>
-      <c r="E14" t="s">
-        <v>282</v>
-      </c>
       <c r="F14" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G14" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H14" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I14" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J14" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -2803,31 +2785,31 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D15" t="s">
+        <v>278</v>
+      </c>
+      <c r="E15" t="s">
         <v>280</v>
       </c>
-      <c r="E15" t="s">
-        <v>282</v>
-      </c>
       <c r="F15" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H15" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I15" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J15" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -2835,31 +2817,31 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D16" t="s">
+        <v>278</v>
+      </c>
+      <c r="E16" t="s">
         <v>280</v>
       </c>
-      <c r="E16" t="s">
-        <v>282</v>
-      </c>
       <c r="F16" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H16" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I16" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="J16" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -2867,31 +2849,31 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C17" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D17" t="s">
+        <v>278</v>
+      </c>
+      <c r="E17" t="s">
         <v>280</v>
       </c>
-      <c r="E17" t="s">
-        <v>282</v>
-      </c>
       <c r="F17" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G17" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H17" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J17" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -2899,31 +2881,31 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C18" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D18" t="s">
+        <v>278</v>
+      </c>
+      <c r="E18" t="s">
         <v>280</v>
       </c>
-      <c r="E18" t="s">
-        <v>282</v>
-      </c>
       <c r="F18" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G18" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I18" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J18" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -2931,31 +2913,31 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D19" t="s">
+        <v>278</v>
+      </c>
+      <c r="E19" t="s">
         <v>280</v>
       </c>
-      <c r="E19" t="s">
-        <v>282</v>
-      </c>
       <c r="F19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G19" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H19" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I19" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J19" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -2963,31 +2945,31 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C20" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D20" t="s">
+        <v>278</v>
+      </c>
+      <c r="E20" t="s">
         <v>280</v>
       </c>
-      <c r="E20" t="s">
-        <v>282</v>
-      </c>
       <c r="F20" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G20" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H20" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J20" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -2995,31 +2977,31 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D21" t="s">
+        <v>278</v>
+      </c>
+      <c r="E21" t="s">
         <v>280</v>
       </c>
-      <c r="E21" t="s">
-        <v>282</v>
-      </c>
       <c r="F21" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G21" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I21" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J21" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -3027,31 +3009,31 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E22" t="s">
+        <v>281</v>
+      </c>
+      <c r="F22" t="s">
+        <v>282</v>
+      </c>
+      <c r="G22" t="s">
         <v>283</v>
       </c>
-      <c r="F22" t="s">
-        <v>284</v>
-      </c>
-      <c r="G22" t="s">
-        <v>285</v>
-      </c>
       <c r="H22" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I22" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="J22" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -3059,31 +3041,31 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C23" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D23" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E23" t="s">
+        <v>281</v>
+      </c>
+      <c r="F23" t="s">
+        <v>282</v>
+      </c>
+      <c r="G23" t="s">
         <v>283</v>
       </c>
-      <c r="F23" t="s">
-        <v>284</v>
-      </c>
-      <c r="G23" t="s">
-        <v>285</v>
-      </c>
       <c r="H23" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I23" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J23" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -3091,31 +3073,31 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C24" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D24" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E24" t="s">
+        <v>281</v>
+      </c>
+      <c r="F24" t="s">
+        <v>282</v>
+      </c>
+      <c r="G24" t="s">
         <v>283</v>
       </c>
-      <c r="F24" t="s">
-        <v>284</v>
-      </c>
-      <c r="G24" t="s">
-        <v>285</v>
-      </c>
       <c r="H24" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I24" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="J24" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -3123,31 +3105,31 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C25" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D25" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E25" t="s">
+        <v>281</v>
+      </c>
+      <c r="F25" t="s">
+        <v>282</v>
+      </c>
+      <c r="G25" t="s">
         <v>283</v>
       </c>
-      <c r="F25" t="s">
-        <v>284</v>
-      </c>
-      <c r="G25" t="s">
-        <v>285</v>
-      </c>
       <c r="H25" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I25" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J25" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -3155,31 +3137,31 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C26" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D26" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E26" t="s">
+        <v>281</v>
+      </c>
+      <c r="F26" t="s">
+        <v>282</v>
+      </c>
+      <c r="G26" t="s">
         <v>283</v>
       </c>
-      <c r="F26" t="s">
-        <v>284</v>
-      </c>
-      <c r="G26" t="s">
-        <v>285</v>
-      </c>
       <c r="H26" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I26" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J26" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -3187,31 +3169,31 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C27" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D27" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E27" t="s">
+        <v>281</v>
+      </c>
+      <c r="F27" t="s">
+        <v>282</v>
+      </c>
+      <c r="G27" t="s">
         <v>283</v>
       </c>
-      <c r="F27" t="s">
-        <v>284</v>
-      </c>
-      <c r="G27" t="s">
-        <v>285</v>
-      </c>
       <c r="H27" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I27" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J27" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -3219,31 +3201,31 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C28" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D28" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E28" t="s">
+        <v>281</v>
+      </c>
+      <c r="F28" t="s">
+        <v>282</v>
+      </c>
+      <c r="G28" t="s">
         <v>283</v>
       </c>
-      <c r="F28" t="s">
-        <v>284</v>
-      </c>
-      <c r="G28" t="s">
-        <v>285</v>
-      </c>
       <c r="H28" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I28" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J28" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -3251,31 +3233,31 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C29" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D29" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E29" t="s">
+        <v>281</v>
+      </c>
+      <c r="F29" t="s">
+        <v>282</v>
+      </c>
+      <c r="G29" t="s">
         <v>283</v>
       </c>
-      <c r="F29" t="s">
-        <v>284</v>
-      </c>
-      <c r="G29" t="s">
-        <v>285</v>
-      </c>
       <c r="H29" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I29" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J29" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -3283,31 +3265,31 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C30" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D30" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E30" t="s">
+        <v>281</v>
+      </c>
+      <c r="F30" t="s">
+        <v>282</v>
+      </c>
+      <c r="G30" t="s">
         <v>283</v>
       </c>
-      <c r="F30" t="s">
-        <v>284</v>
-      </c>
-      <c r="G30" t="s">
-        <v>285</v>
-      </c>
       <c r="H30" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I30" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J30" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
@@ -3315,31 +3297,31 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C31" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D31" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E31" t="s">
+        <v>281</v>
+      </c>
+      <c r="F31" t="s">
+        <v>282</v>
+      </c>
+      <c r="G31" t="s">
         <v>283</v>
       </c>
-      <c r="F31" t="s">
-        <v>284</v>
-      </c>
-      <c r="G31" t="s">
-        <v>285</v>
-      </c>
       <c r="H31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I31" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J31" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
@@ -3347,31 +3329,31 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C32" t="s">
+        <v>277</v>
+      </c>
+      <c r="D32" t="s">
+        <v>278</v>
+      </c>
+      <c r="E32" t="s">
         <v>279</v>
       </c>
-      <c r="D32" t="s">
-        <v>280</v>
-      </c>
-      <c r="E32" t="s">
-        <v>281</v>
-      </c>
       <c r="F32" t="s">
+        <v>282</v>
+      </c>
+      <c r="G32" t="s">
         <v>284</v>
       </c>
-      <c r="G32" t="s">
-        <v>286</v>
-      </c>
       <c r="H32" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I32" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J32" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
@@ -3379,31 +3361,31 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C33" t="s">
+        <v>277</v>
+      </c>
+      <c r="D33" t="s">
+        <v>278</v>
+      </c>
+      <c r="E33" t="s">
         <v>279</v>
       </c>
-      <c r="D33" t="s">
-        <v>280</v>
-      </c>
-      <c r="E33" t="s">
-        <v>281</v>
-      </c>
       <c r="F33" t="s">
+        <v>282</v>
+      </c>
+      <c r="G33" t="s">
         <v>284</v>
       </c>
-      <c r="G33" t="s">
-        <v>286</v>
-      </c>
       <c r="H33" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I33" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J33" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -3411,31 +3393,31 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C34" t="s">
+        <v>277</v>
+      </c>
+      <c r="D34" t="s">
+        <v>278</v>
+      </c>
+      <c r="E34" t="s">
         <v>279</v>
       </c>
-      <c r="D34" t="s">
-        <v>280</v>
-      </c>
-      <c r="E34" t="s">
-        <v>281</v>
-      </c>
       <c r="F34" t="s">
+        <v>282</v>
+      </c>
+      <c r="G34" t="s">
         <v>284</v>
       </c>
-      <c r="G34" t="s">
-        <v>286</v>
-      </c>
       <c r="H34" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I34" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="J34" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -3443,31 +3425,31 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C35" t="s">
+        <v>277</v>
+      </c>
+      <c r="D35" t="s">
+        <v>278</v>
+      </c>
+      <c r="E35" t="s">
         <v>279</v>
       </c>
-      <c r="D35" t="s">
-        <v>280</v>
-      </c>
-      <c r="E35" t="s">
-        <v>281</v>
-      </c>
       <c r="F35" t="s">
+        <v>282</v>
+      </c>
+      <c r="G35" t="s">
         <v>284</v>
       </c>
-      <c r="G35" t="s">
-        <v>286</v>
-      </c>
       <c r="H35" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I35" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J35" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -3475,31 +3457,31 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C36" t="s">
+        <v>277</v>
+      </c>
+      <c r="D36" t="s">
+        <v>278</v>
+      </c>
+      <c r="E36" t="s">
         <v>279</v>
       </c>
-      <c r="D36" t="s">
-        <v>280</v>
-      </c>
-      <c r="E36" t="s">
-        <v>281</v>
-      </c>
       <c r="F36" t="s">
+        <v>282</v>
+      </c>
+      <c r="G36" t="s">
         <v>284</v>
       </c>
-      <c r="G36" t="s">
-        <v>286</v>
-      </c>
       <c r="H36" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I36" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J36" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -3507,31 +3489,31 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C37" t="s">
+        <v>277</v>
+      </c>
+      <c r="D37" t="s">
+        <v>278</v>
+      </c>
+      <c r="E37" t="s">
         <v>279</v>
       </c>
-      <c r="D37" t="s">
-        <v>280</v>
-      </c>
-      <c r="E37" t="s">
-        <v>281</v>
-      </c>
       <c r="F37" t="s">
+        <v>282</v>
+      </c>
+      <c r="G37" t="s">
         <v>284</v>
       </c>
-      <c r="G37" t="s">
-        <v>286</v>
-      </c>
       <c r="H37" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I37" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J37" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -3539,31 +3521,31 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C38" t="s">
+        <v>277</v>
+      </c>
+      <c r="D38" t="s">
+        <v>278</v>
+      </c>
+      <c r="E38" t="s">
         <v>279</v>
       </c>
-      <c r="D38" t="s">
-        <v>280</v>
-      </c>
-      <c r="E38" t="s">
-        <v>281</v>
-      </c>
       <c r="F38" t="s">
+        <v>282</v>
+      </c>
+      <c r="G38" t="s">
         <v>284</v>
       </c>
-      <c r="G38" t="s">
-        <v>286</v>
-      </c>
       <c r="H38" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I38" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J38" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -3571,31 +3553,31 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C39" t="s">
+        <v>277</v>
+      </c>
+      <c r="D39" t="s">
+        <v>278</v>
+      </c>
+      <c r="E39" t="s">
         <v>279</v>
       </c>
-      <c r="D39" t="s">
-        <v>280</v>
-      </c>
-      <c r="E39" t="s">
-        <v>281</v>
-      </c>
       <c r="F39" t="s">
+        <v>282</v>
+      </c>
+      <c r="G39" t="s">
         <v>284</v>
       </c>
-      <c r="G39" t="s">
-        <v>286</v>
-      </c>
       <c r="H39" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I39" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J39" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
@@ -3603,31 +3585,31 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C40" t="s">
+        <v>277</v>
+      </c>
+      <c r="D40" t="s">
+        <v>278</v>
+      </c>
+      <c r="E40" t="s">
         <v>279</v>
       </c>
-      <c r="D40" t="s">
-        <v>280</v>
-      </c>
-      <c r="E40" t="s">
-        <v>281</v>
-      </c>
       <c r="F40" t="s">
+        <v>282</v>
+      </c>
+      <c r="G40" t="s">
         <v>284</v>
       </c>
-      <c r="G40" t="s">
-        <v>286</v>
-      </c>
       <c r="H40" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I40" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J40" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
@@ -3635,31 +3617,31 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C41" t="s">
+        <v>277</v>
+      </c>
+      <c r="D41" t="s">
+        <v>278</v>
+      </c>
+      <c r="E41" t="s">
         <v>279</v>
       </c>
-      <c r="D41" t="s">
-        <v>280</v>
-      </c>
-      <c r="E41" t="s">
-        <v>281</v>
-      </c>
       <c r="F41" t="s">
+        <v>282</v>
+      </c>
+      <c r="G41" t="s">
         <v>284</v>
       </c>
-      <c r="G41" t="s">
-        <v>286</v>
-      </c>
       <c r="H41" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I41" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J41" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
@@ -3667,31 +3649,31 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C42" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D42" t="s">
+        <v>278</v>
+      </c>
+      <c r="E42" t="s">
         <v>280</v>
       </c>
-      <c r="E42" t="s">
-        <v>282</v>
-      </c>
       <c r="F42" t="s">
+        <v>282</v>
+      </c>
+      <c r="G42" t="s">
         <v>284</v>
       </c>
-      <c r="G42" t="s">
-        <v>286</v>
-      </c>
       <c r="H42" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I42" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J42" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
@@ -3699,31 +3681,31 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C43" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D43" t="s">
+        <v>278</v>
+      </c>
+      <c r="E43" t="s">
         <v>280</v>
       </c>
-      <c r="E43" t="s">
-        <v>282</v>
-      </c>
       <c r="F43" t="s">
+        <v>282</v>
+      </c>
+      <c r="G43" t="s">
         <v>284</v>
       </c>
-      <c r="G43" t="s">
-        <v>286</v>
-      </c>
       <c r="H43" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I43" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J43" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -3731,31 +3713,31 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C44" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D44" t="s">
+        <v>278</v>
+      </c>
+      <c r="E44" t="s">
         <v>280</v>
       </c>
-      <c r="E44" t="s">
-        <v>282</v>
-      </c>
       <c r="F44" t="s">
+        <v>282</v>
+      </c>
+      <c r="G44" t="s">
         <v>284</v>
       </c>
-      <c r="G44" t="s">
-        <v>286</v>
-      </c>
       <c r="H44" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I44" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J44" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
@@ -3763,31 +3745,31 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C45" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D45" t="s">
+        <v>278</v>
+      </c>
+      <c r="E45" t="s">
         <v>280</v>
       </c>
-      <c r="E45" t="s">
-        <v>282</v>
-      </c>
       <c r="F45" t="s">
+        <v>282</v>
+      </c>
+      <c r="G45" t="s">
         <v>284</v>
       </c>
-      <c r="G45" t="s">
-        <v>286</v>
-      </c>
       <c r="H45" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J45" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
@@ -3795,31 +3777,31 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C46" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D46" t="s">
+        <v>278</v>
+      </c>
+      <c r="E46" t="s">
         <v>280</v>
       </c>
-      <c r="E46" t="s">
-        <v>282</v>
-      </c>
       <c r="F46" t="s">
+        <v>282</v>
+      </c>
+      <c r="G46" t="s">
         <v>284</v>
       </c>
-      <c r="G46" t="s">
-        <v>286</v>
-      </c>
       <c r="H46" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I46" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J46" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -3827,31 +3809,31 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C47" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D47" t="s">
+        <v>278</v>
+      </c>
+      <c r="E47" t="s">
         <v>280</v>
       </c>
-      <c r="E47" t="s">
-        <v>282</v>
-      </c>
       <c r="F47" t="s">
+        <v>282</v>
+      </c>
+      <c r="G47" t="s">
         <v>284</v>
       </c>
-      <c r="G47" t="s">
-        <v>286</v>
-      </c>
       <c r="H47" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I47" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J47" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
@@ -3859,31 +3841,31 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C48" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D48" t="s">
+        <v>278</v>
+      </c>
+      <c r="E48" t="s">
         <v>280</v>
       </c>
-      <c r="E48" t="s">
-        <v>282</v>
-      </c>
       <c r="F48" t="s">
+        <v>282</v>
+      </c>
+      <c r="G48" t="s">
         <v>284</v>
       </c>
-      <c r="G48" t="s">
-        <v>286</v>
-      </c>
       <c r="H48" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I48" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J48" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
@@ -3891,31 +3873,31 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C49" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D49" t="s">
+        <v>278</v>
+      </c>
+      <c r="E49" t="s">
         <v>280</v>
       </c>
-      <c r="E49" t="s">
-        <v>282</v>
-      </c>
       <c r="F49" t="s">
+        <v>282</v>
+      </c>
+      <c r="G49" t="s">
         <v>284</v>
       </c>
-      <c r="G49" t="s">
-        <v>286</v>
-      </c>
       <c r="H49" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I49" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="J49" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
@@ -3923,31 +3905,31 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C50" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D50" t="s">
+        <v>278</v>
+      </c>
+      <c r="E50" t="s">
         <v>280</v>
       </c>
-      <c r="E50" t="s">
-        <v>282</v>
-      </c>
       <c r="F50" t="s">
+        <v>282</v>
+      </c>
+      <c r="G50" t="s">
         <v>284</v>
       </c>
-      <c r="G50" t="s">
-        <v>286</v>
-      </c>
       <c r="H50" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I50" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J50" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
@@ -3955,31 +3937,31 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C51" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D51" t="s">
+        <v>278</v>
+      </c>
+      <c r="E51" t="s">
         <v>280</v>
       </c>
-      <c r="E51" t="s">
-        <v>282</v>
-      </c>
       <c r="F51" t="s">
+        <v>282</v>
+      </c>
+      <c r="G51" t="s">
         <v>284</v>
       </c>
-      <c r="G51" t="s">
-        <v>286</v>
-      </c>
       <c r="H51" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I51" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="J51" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
@@ -3987,31 +3969,31 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C52" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D52" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E52" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F52" t="s">
+        <v>282</v>
+      </c>
+      <c r="G52" t="s">
         <v>284</v>
       </c>
-      <c r="G52" t="s">
-        <v>286</v>
-      </c>
       <c r="H52" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I52" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="J52" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
@@ -4019,31 +4001,31 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C53" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D53" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E53" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F53" t="s">
+        <v>282</v>
+      </c>
+      <c r="G53" t="s">
         <v>284</v>
       </c>
-      <c r="G53" t="s">
-        <v>286</v>
-      </c>
       <c r="H53" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I53" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="J53" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
@@ -4051,31 +4033,31 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C54" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D54" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E54" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F54" t="s">
+        <v>282</v>
+      </c>
+      <c r="G54" t="s">
         <v>284</v>
       </c>
-      <c r="G54" t="s">
-        <v>286</v>
-      </c>
       <c r="H54" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I54" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J54" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
@@ -4083,31 +4065,31 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C55" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D55" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E55" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F55" t="s">
+        <v>282</v>
+      </c>
+      <c r="G55" t="s">
         <v>284</v>
       </c>
-      <c r="G55" t="s">
-        <v>286</v>
-      </c>
       <c r="H55" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I55" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J55" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
@@ -4115,31 +4097,31 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C56" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D56" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E56" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F56" t="s">
+        <v>282</v>
+      </c>
+      <c r="G56" t="s">
         <v>284</v>
       </c>
-      <c r="G56" t="s">
-        <v>286</v>
-      </c>
       <c r="H56" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I56" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J56" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
@@ -4147,31 +4129,31 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C57" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D57" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E57" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F57" t="s">
+        <v>282</v>
+      </c>
+      <c r="G57" t="s">
         <v>284</v>
       </c>
-      <c r="G57" t="s">
-        <v>286</v>
-      </c>
       <c r="H57" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I57" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J57" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
@@ -4179,31 +4161,31 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C58" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D58" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E58" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F58" t="s">
+        <v>282</v>
+      </c>
+      <c r="G58" t="s">
         <v>284</v>
       </c>
-      <c r="G58" t="s">
-        <v>286</v>
-      </c>
       <c r="H58" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I58" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J58" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
@@ -4211,31 +4193,31 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C59" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D59" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E59" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F59" t="s">
+        <v>282</v>
+      </c>
+      <c r="G59" t="s">
         <v>284</v>
       </c>
-      <c r="G59" t="s">
-        <v>286</v>
-      </c>
       <c r="H59" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I59" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J59" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
@@ -4243,31 +4225,31 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C60" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D60" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E60" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F60" t="s">
+        <v>282</v>
+      </c>
+      <c r="G60" t="s">
         <v>284</v>
       </c>
-      <c r="G60" t="s">
-        <v>286</v>
-      </c>
       <c r="H60" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I60" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J60" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
@@ -4275,31 +4257,31 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C61" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D61" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E61" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F61" t="s">
+        <v>282</v>
+      </c>
+      <c r="G61" t="s">
         <v>284</v>
       </c>
-      <c r="G61" t="s">
-        <v>286</v>
-      </c>
       <c r="H61" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I61" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J61" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
@@ -4307,31 +4289,31 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C62" t="s">
+        <v>277</v>
+      </c>
+      <c r="D62" t="s">
+        <v>278</v>
+      </c>
+      <c r="E62" t="s">
         <v>279</v>
       </c>
-      <c r="D62" t="s">
-        <v>280</v>
-      </c>
-      <c r="E62" t="s">
-        <v>281</v>
-      </c>
       <c r="F62" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G62" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H62" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I62" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J62" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
@@ -4339,31 +4321,31 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C63" t="s">
+        <v>277</v>
+      </c>
+      <c r="D63" t="s">
+        <v>278</v>
+      </c>
+      <c r="E63" t="s">
         <v>279</v>
       </c>
-      <c r="D63" t="s">
-        <v>280</v>
-      </c>
-      <c r="E63" t="s">
-        <v>281</v>
-      </c>
       <c r="F63" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G63" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H63" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I63" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J63" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
@@ -4371,31 +4353,31 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C64" t="s">
+        <v>277</v>
+      </c>
+      <c r="D64" t="s">
+        <v>278</v>
+      </c>
+      <c r="E64" t="s">
         <v>279</v>
       </c>
-      <c r="D64" t="s">
-        <v>280</v>
-      </c>
-      <c r="E64" t="s">
-        <v>281</v>
-      </c>
       <c r="F64" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G64" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H64" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I64" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J64" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
@@ -4403,31 +4385,31 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C65" t="s">
+        <v>277</v>
+      </c>
+      <c r="D65" t="s">
+        <v>278</v>
+      </c>
+      <c r="E65" t="s">
         <v>279</v>
       </c>
-      <c r="D65" t="s">
-        <v>280</v>
-      </c>
-      <c r="E65" t="s">
-        <v>281</v>
-      </c>
       <c r="F65" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G65" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H65" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I65" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J65" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
@@ -4435,31 +4417,31 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C66" t="s">
+        <v>277</v>
+      </c>
+      <c r="D66" t="s">
+        <v>278</v>
+      </c>
+      <c r="E66" t="s">
         <v>279</v>
       </c>
-      <c r="D66" t="s">
-        <v>280</v>
-      </c>
-      <c r="E66" t="s">
-        <v>281</v>
-      </c>
       <c r="F66" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G66" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H66" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I66" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J66" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
@@ -4467,31 +4449,31 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C67" t="s">
+        <v>277</v>
+      </c>
+      <c r="D67" t="s">
+        <v>278</v>
+      </c>
+      <c r="E67" t="s">
         <v>279</v>
       </c>
-      <c r="D67" t="s">
-        <v>280</v>
-      </c>
-      <c r="E67" t="s">
-        <v>281</v>
-      </c>
       <c r="F67" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G67" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H67" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I67" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J67" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
@@ -4499,31 +4481,31 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C68" t="s">
+        <v>277</v>
+      </c>
+      <c r="D68" t="s">
+        <v>278</v>
+      </c>
+      <c r="E68" t="s">
         <v>279</v>
       </c>
-      <c r="D68" t="s">
-        <v>280</v>
-      </c>
-      <c r="E68" t="s">
-        <v>281</v>
-      </c>
       <c r="F68" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G68" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H68" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I68" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J68" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
@@ -4531,31 +4513,31 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C69" t="s">
+        <v>277</v>
+      </c>
+      <c r="D69" t="s">
+        <v>278</v>
+      </c>
+      <c r="E69" t="s">
         <v>279</v>
       </c>
-      <c r="D69" t="s">
-        <v>280</v>
-      </c>
-      <c r="E69" t="s">
-        <v>281</v>
-      </c>
       <c r="F69" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G69" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H69" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I69" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J69" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
@@ -4563,31 +4545,31 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C70" t="s">
+        <v>277</v>
+      </c>
+      <c r="D70" t="s">
+        <v>278</v>
+      </c>
+      <c r="E70" t="s">
         <v>279</v>
       </c>
-      <c r="D70" t="s">
-        <v>280</v>
-      </c>
-      <c r="E70" t="s">
-        <v>281</v>
-      </c>
       <c r="F70" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G70" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H70" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I70" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J70" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
@@ -4595,31 +4577,31 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C71" t="s">
+        <v>277</v>
+      </c>
+      <c r="D71" t="s">
+        <v>278</v>
+      </c>
+      <c r="E71" t="s">
         <v>279</v>
       </c>
-      <c r="D71" t="s">
-        <v>280</v>
-      </c>
-      <c r="E71" t="s">
-        <v>281</v>
-      </c>
       <c r="F71" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G71" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H71" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I71" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J71" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
@@ -4627,31 +4609,31 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C72" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D72" t="s">
+        <v>278</v>
+      </c>
+      <c r="E72" t="s">
         <v>280</v>
       </c>
-      <c r="E72" t="s">
-        <v>282</v>
-      </c>
       <c r="F72" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G72" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H72" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I72" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J72" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
@@ -4659,31 +4641,31 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C73" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D73" t="s">
+        <v>278</v>
+      </c>
+      <c r="E73" t="s">
         <v>280</v>
       </c>
-      <c r="E73" t="s">
-        <v>282</v>
-      </c>
       <c r="F73" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G73" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H73" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I73" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J73" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
@@ -4691,31 +4673,31 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C74" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D74" t="s">
+        <v>278</v>
+      </c>
+      <c r="E74" t="s">
         <v>280</v>
       </c>
-      <c r="E74" t="s">
-        <v>282</v>
-      </c>
       <c r="F74" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G74" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H74" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I74" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J74" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
@@ -4723,31 +4705,31 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C75" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D75" t="s">
+        <v>278</v>
+      </c>
+      <c r="E75" t="s">
         <v>280</v>
       </c>
-      <c r="E75" t="s">
-        <v>282</v>
-      </c>
       <c r="F75" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G75" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H75" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I75" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J75" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
@@ -4755,31 +4737,31 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C76" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D76" t="s">
+        <v>278</v>
+      </c>
+      <c r="E76" t="s">
         <v>280</v>
       </c>
-      <c r="E76" t="s">
-        <v>282</v>
-      </c>
       <c r="F76" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G76" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H76" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I76" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J76" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
@@ -4787,31 +4769,31 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C77" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D77" t="s">
+        <v>278</v>
+      </c>
+      <c r="E77" t="s">
         <v>280</v>
       </c>
-      <c r="E77" t="s">
-        <v>282</v>
-      </c>
       <c r="F77" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G77" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H77" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I77" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J77" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
@@ -4819,31 +4801,31 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C78" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D78" t="s">
+        <v>278</v>
+      </c>
+      <c r="E78" t="s">
         <v>280</v>
       </c>
-      <c r="E78" t="s">
-        <v>282</v>
-      </c>
       <c r="F78" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G78" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H78" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I78" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J78" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
@@ -4851,31 +4833,31 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C79" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D79" t="s">
+        <v>278</v>
+      </c>
+      <c r="E79" t="s">
         <v>280</v>
       </c>
-      <c r="E79" t="s">
-        <v>282</v>
-      </c>
       <c r="F79" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G79" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H79" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I79" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J79" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
@@ -4883,31 +4865,31 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C80" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D80" t="s">
+        <v>278</v>
+      </c>
+      <c r="E80" t="s">
         <v>280</v>
       </c>
-      <c r="E80" t="s">
-        <v>282</v>
-      </c>
       <c r="F80" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G80" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H80" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I80" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J80" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
@@ -4915,31 +4897,31 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C81" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D81" t="s">
+        <v>278</v>
+      </c>
+      <c r="E81" t="s">
         <v>280</v>
       </c>
-      <c r="E81" t="s">
-        <v>282</v>
-      </c>
       <c r="F81" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G81" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H81" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I81" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J81" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
@@ -4947,31 +4929,31 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C82" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D82" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E82" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F82" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G82" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H82" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I82" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="J82" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
@@ -4979,31 +4961,31 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C83" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D83" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E83" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F83" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G83" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H83" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I83" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J83" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
@@ -5011,31 +4993,31 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C84" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D84" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E84" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F84" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G84" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H84" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I84" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J84" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
@@ -5043,31 +5025,31 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C85" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D85" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E85" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F85" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G85" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H85" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I85" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J85" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
@@ -5075,31 +5057,31 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C86" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D86" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E86" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F86" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G86" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H86" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I86" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J86" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
@@ -5107,31 +5089,31 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C87" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D87" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E87" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F87" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G87" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H87" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I87" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J87" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
@@ -5139,31 +5121,31 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C88" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D88" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E88" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F88" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G88" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H88" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I88" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J88" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
@@ -5171,31 +5153,31 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C89" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D89" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E89" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F89" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G89" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H89" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I89" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J89" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
@@ -5203,31 +5185,31 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C90" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D90" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E90" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F90" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G90" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H90" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I90" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J90" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
@@ -5235,31 +5217,31 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C91" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D91" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E91" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F91" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G91" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H91" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I91" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J91" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
@@ -5267,31 +5249,31 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C92" t="s">
+        <v>277</v>
+      </c>
+      <c r="D92" t="s">
+        <v>278</v>
+      </c>
+      <c r="E92" t="s">
         <v>279</v>
       </c>
-      <c r="D92" t="s">
-        <v>280</v>
-      </c>
-      <c r="E92" t="s">
-        <v>281</v>
-      </c>
       <c r="F92" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G92" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H92" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I92" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J92" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
@@ -5299,31 +5281,31 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C93" t="s">
+        <v>277</v>
+      </c>
+      <c r="D93" t="s">
+        <v>278</v>
+      </c>
+      <c r="E93" t="s">
         <v>279</v>
       </c>
-      <c r="D93" t="s">
-        <v>280</v>
-      </c>
-      <c r="E93" t="s">
-        <v>281</v>
-      </c>
       <c r="F93" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G93" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H93" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I93" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J93" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
@@ -5331,31 +5313,31 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C94" t="s">
+        <v>277</v>
+      </c>
+      <c r="D94" t="s">
+        <v>278</v>
+      </c>
+      <c r="E94" t="s">
         <v>279</v>
       </c>
-      <c r="D94" t="s">
-        <v>280</v>
-      </c>
-      <c r="E94" t="s">
-        <v>281</v>
-      </c>
       <c r="F94" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G94" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H94" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I94" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J94" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
@@ -5363,31 +5345,31 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C95" t="s">
+        <v>277</v>
+      </c>
+      <c r="D95" t="s">
+        <v>278</v>
+      </c>
+      <c r="E95" t="s">
         <v>279</v>
       </c>
-      <c r="D95" t="s">
-        <v>280</v>
-      </c>
-      <c r="E95" t="s">
-        <v>281</v>
-      </c>
       <c r="F95" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G95" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H95" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I95" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J95" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
@@ -5395,31 +5377,31 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C96" t="s">
+        <v>277</v>
+      </c>
+      <c r="D96" t="s">
+        <v>278</v>
+      </c>
+      <c r="E96" t="s">
         <v>279</v>
       </c>
-      <c r="D96" t="s">
-        <v>280</v>
-      </c>
-      <c r="E96" t="s">
-        <v>281</v>
-      </c>
       <c r="F96" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G96" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H96" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I96" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J96" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
@@ -5427,31 +5409,31 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C97" t="s">
+        <v>277</v>
+      </c>
+      <c r="D97" t="s">
+        <v>278</v>
+      </c>
+      <c r="E97" t="s">
         <v>279</v>
       </c>
-      <c r="D97" t="s">
-        <v>280</v>
-      </c>
-      <c r="E97" t="s">
-        <v>281</v>
-      </c>
       <c r="F97" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G97" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H97" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I97" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J97" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
@@ -5459,31 +5441,31 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C98" t="s">
+        <v>277</v>
+      </c>
+      <c r="D98" t="s">
+        <v>278</v>
+      </c>
+      <c r="E98" t="s">
         <v>279</v>
       </c>
-      <c r="D98" t="s">
-        <v>280</v>
-      </c>
-      <c r="E98" t="s">
-        <v>281</v>
-      </c>
       <c r="F98" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G98" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H98" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I98" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J98" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
@@ -5491,31 +5473,31 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C99" t="s">
+        <v>277</v>
+      </c>
+      <c r="D99" t="s">
+        <v>278</v>
+      </c>
+      <c r="E99" t="s">
         <v>279</v>
       </c>
-      <c r="D99" t="s">
-        <v>280</v>
-      </c>
-      <c r="E99" t="s">
-        <v>281</v>
-      </c>
       <c r="F99" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G99" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H99" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I99" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J99" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
@@ -5523,31 +5505,31 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C100" t="s">
+        <v>277</v>
+      </c>
+      <c r="D100" t="s">
+        <v>278</v>
+      </c>
+      <c r="E100" t="s">
         <v>279</v>
       </c>
-      <c r="D100" t="s">
-        <v>280</v>
-      </c>
-      <c r="E100" t="s">
-        <v>281</v>
-      </c>
       <c r="F100" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G100" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H100" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I100" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J100" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
@@ -5555,31 +5537,31 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C101" t="s">
+        <v>277</v>
+      </c>
+      <c r="D101" t="s">
+        <v>278</v>
+      </c>
+      <c r="E101" t="s">
         <v>279</v>
       </c>
-      <c r="D101" t="s">
-        <v>280</v>
-      </c>
-      <c r="E101" t="s">
-        <v>281</v>
-      </c>
       <c r="F101" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G101" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H101" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I101" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J101" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
@@ -5587,31 +5569,31 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C102" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D102" t="s">
+        <v>278</v>
+      </c>
+      <c r="E102" t="s">
         <v>280</v>
       </c>
-      <c r="E102" t="s">
-        <v>282</v>
-      </c>
       <c r="F102" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G102" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H102" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I102" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J102" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
@@ -5619,31 +5601,31 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C103" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D103" t="s">
+        <v>278</v>
+      </c>
+      <c r="E103" t="s">
         <v>280</v>
       </c>
-      <c r="E103" t="s">
-        <v>282</v>
-      </c>
       <c r="F103" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G103" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H103" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I103" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J103" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
@@ -5651,31 +5633,31 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C104" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D104" t="s">
+        <v>278</v>
+      </c>
+      <c r="E104" t="s">
         <v>280</v>
       </c>
-      <c r="E104" t="s">
-        <v>282</v>
-      </c>
       <c r="F104" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G104" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H104" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I104" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J104" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
@@ -5683,31 +5665,31 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C105" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D105" t="s">
+        <v>278</v>
+      </c>
+      <c r="E105" t="s">
         <v>280</v>
       </c>
-      <c r="E105" t="s">
-        <v>282</v>
-      </c>
       <c r="F105" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G105" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H105" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I105" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="J105" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.2">
@@ -5715,31 +5697,31 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C106" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D106" t="s">
+        <v>278</v>
+      </c>
+      <c r="E106" t="s">
         <v>280</v>
       </c>
-      <c r="E106" t="s">
-        <v>282</v>
-      </c>
       <c r="F106" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G106" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H106" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I106" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J106" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
@@ -5747,31 +5729,31 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C107" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D107" t="s">
+        <v>278</v>
+      </c>
+      <c r="E107" t="s">
         <v>280</v>
       </c>
-      <c r="E107" t="s">
-        <v>282</v>
-      </c>
       <c r="F107" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G107" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H107" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I107" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="J107" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.2">
@@ -5779,31 +5761,31 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C108" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D108" t="s">
+        <v>278</v>
+      </c>
+      <c r="E108" t="s">
         <v>280</v>
       </c>
-      <c r="E108" t="s">
-        <v>282</v>
-      </c>
       <c r="F108" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G108" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H108" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I108" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J108" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.2">
@@ -5811,31 +5793,31 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C109" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D109" t="s">
+        <v>278</v>
+      </c>
+      <c r="E109" t="s">
         <v>280</v>
       </c>
-      <c r="E109" t="s">
-        <v>282</v>
-      </c>
       <c r="F109" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G109" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H109" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I109" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="J109" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.2">
@@ -5843,31 +5825,31 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C110" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D110" t="s">
+        <v>278</v>
+      </c>
+      <c r="E110" t="s">
         <v>280</v>
       </c>
-      <c r="E110" t="s">
-        <v>282</v>
-      </c>
       <c r="F110" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G110" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H110" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I110" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J110" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
@@ -5875,31 +5857,31 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C111" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D111" t="s">
+        <v>278</v>
+      </c>
+      <c r="E111" t="s">
         <v>280</v>
       </c>
-      <c r="E111" t="s">
-        <v>282</v>
-      </c>
       <c r="F111" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G111" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H111" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I111" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J111" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.2">
@@ -5907,31 +5889,31 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C112" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D112" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E112" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F112" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G112" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H112" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I112" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="J112" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.2">
@@ -5939,31 +5921,31 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C113" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D113" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F113" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G113" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H113" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I113" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J113" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.2">
@@ -5971,31 +5953,31 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C114" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D114" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F114" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G114" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H114" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I114" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J114" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.2">
@@ -6003,31 +5985,31 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C115" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D115" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F115" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G115" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H115" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I115" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="J115" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.2">
@@ -6035,31 +6017,31 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C116" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D116" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E116" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F116" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G116" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H116" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I116" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J116" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.2">
@@ -6067,31 +6049,31 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C117" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D117" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F117" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G117" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H117" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I117" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="J117" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.2">
@@ -6099,31 +6081,31 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C118" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D118" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F118" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G118" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H118" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I118" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="J118" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
@@ -6131,31 +6113,31 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C119" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D119" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F119" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G119" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H119" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I119" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J119" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.2">
@@ -6163,31 +6145,31 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C120" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D120" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E120" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F120" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G120" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H120" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I120" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J120" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.2">
@@ -6195,31 +6177,31 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C121" t="s">
+        <v>277</v>
+      </c>
+      <c r="D121" t="s">
+        <v>278</v>
+      </c>
+      <c r="E121" t="s">
         <v>279</v>
       </c>
-      <c r="D121" t="s">
-        <v>280</v>
-      </c>
-      <c r="E121" t="s">
-        <v>283</v>
-      </c>
       <c r="F121" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G121" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H121" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I121" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J121" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.2">
@@ -6227,31 +6209,31 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C122" t="s">
+        <v>277</v>
+      </c>
+      <c r="D122" t="s">
+        <v>278</v>
+      </c>
+      <c r="E122" t="s">
         <v>279</v>
       </c>
-      <c r="D122" t="s">
-        <v>280</v>
-      </c>
-      <c r="E122" t="s">
-        <v>281</v>
-      </c>
       <c r="F122" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G122" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H122" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I122" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J122" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.2">
@@ -6259,31 +6241,31 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C123" t="s">
+        <v>277</v>
+      </c>
+      <c r="D123" t="s">
+        <v>278</v>
+      </c>
+      <c r="E123" t="s">
         <v>279</v>
       </c>
-      <c r="D123" t="s">
-        <v>280</v>
-      </c>
-      <c r="E123" t="s">
-        <v>281</v>
-      </c>
       <c r="F123" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G123" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H123" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I123" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="J123" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.2">
@@ -6291,31 +6273,31 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C124" t="s">
+        <v>277</v>
+      </c>
+      <c r="D124" t="s">
+        <v>278</v>
+      </c>
+      <c r="E124" t="s">
         <v>279</v>
       </c>
-      <c r="D124" t="s">
-        <v>280</v>
-      </c>
-      <c r="E124" t="s">
-        <v>281</v>
-      </c>
       <c r="F124" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G124" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H124" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I124" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J124" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.2">
@@ -6323,31 +6305,31 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C125" t="s">
+        <v>277</v>
+      </c>
+      <c r="D125" t="s">
+        <v>278</v>
+      </c>
+      <c r="E125" t="s">
         <v>279</v>
       </c>
-      <c r="D125" t="s">
-        <v>280</v>
-      </c>
-      <c r="E125" t="s">
-        <v>281</v>
-      </c>
       <c r="F125" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G125" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H125" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I125" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J125" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.2">
@@ -6355,31 +6337,31 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C126" t="s">
+        <v>277</v>
+      </c>
+      <c r="D126" t="s">
+        <v>278</v>
+      </c>
+      <c r="E126" t="s">
         <v>279</v>
       </c>
-      <c r="D126" t="s">
-        <v>280</v>
-      </c>
-      <c r="E126" t="s">
-        <v>281</v>
-      </c>
       <c r="F126" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G126" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H126" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I126" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J126" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.2">
@@ -6387,31 +6369,31 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C127" t="s">
+        <v>277</v>
+      </c>
+      <c r="D127" t="s">
+        <v>278</v>
+      </c>
+      <c r="E127" t="s">
         <v>279</v>
       </c>
-      <c r="D127" t="s">
-        <v>280</v>
-      </c>
-      <c r="E127" t="s">
-        <v>281</v>
-      </c>
       <c r="F127" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G127" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H127" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I127" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="J127" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.2">
@@ -6419,31 +6401,31 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C128" t="s">
+        <v>277</v>
+      </c>
+      <c r="D128" t="s">
+        <v>278</v>
+      </c>
+      <c r="E128" t="s">
         <v>279</v>
       </c>
-      <c r="D128" t="s">
-        <v>280</v>
-      </c>
-      <c r="E128" t="s">
-        <v>281</v>
-      </c>
       <c r="F128" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G128" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H128" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I128" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J128" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
@@ -6451,31 +6433,31 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C129" t="s">
+        <v>277</v>
+      </c>
+      <c r="D129" t="s">
+        <v>278</v>
+      </c>
+      <c r="E129" t="s">
         <v>279</v>
       </c>
-      <c r="D129" t="s">
-        <v>280</v>
-      </c>
-      <c r="E129" t="s">
-        <v>281</v>
-      </c>
       <c r="F129" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G129" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H129" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I129" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J129" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
@@ -6483,31 +6465,31 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C130" t="s">
+        <v>277</v>
+      </c>
+      <c r="D130" t="s">
+        <v>278</v>
+      </c>
+      <c r="E130" t="s">
         <v>279</v>
       </c>
-      <c r="D130" t="s">
-        <v>280</v>
-      </c>
-      <c r="E130" t="s">
-        <v>281</v>
-      </c>
       <c r="F130" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G130" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H130" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I130" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J130" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
@@ -6515,31 +6497,31 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C131" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D131" t="s">
+        <v>278</v>
+      </c>
+      <c r="E131" t="s">
         <v>280</v>
       </c>
-      <c r="E131" t="s">
-        <v>281</v>
-      </c>
       <c r="F131" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G131" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H131" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I131" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="J131" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
@@ -6547,31 +6529,31 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C132" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D132" t="s">
+        <v>278</v>
+      </c>
+      <c r="E132" t="s">
         <v>280</v>
       </c>
-      <c r="E132" t="s">
-        <v>282</v>
-      </c>
       <c r="F132" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G132" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H132" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I132" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J132" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
@@ -6579,31 +6561,31 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C133" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D133" t="s">
+        <v>278</v>
+      </c>
+      <c r="E133" t="s">
         <v>280</v>
       </c>
-      <c r="E133" t="s">
-        <v>282</v>
-      </c>
       <c r="F133" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G133" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H133" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I133" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J133" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
@@ -6611,31 +6593,31 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C134" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D134" t="s">
+        <v>278</v>
+      </c>
+      <c r="E134" t="s">
         <v>280</v>
       </c>
-      <c r="E134" t="s">
-        <v>282</v>
-      </c>
       <c r="F134" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G134" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H134" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I134" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J134" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
@@ -6643,31 +6625,31 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C135" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D135" t="s">
+        <v>278</v>
+      </c>
+      <c r="E135" t="s">
         <v>280</v>
       </c>
-      <c r="E135" t="s">
-        <v>282</v>
-      </c>
       <c r="F135" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G135" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H135" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I135" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J135" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.2">
@@ -6675,31 +6657,31 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C136" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D136" t="s">
+        <v>278</v>
+      </c>
+      <c r="E136" t="s">
         <v>280</v>
       </c>
-      <c r="E136" t="s">
-        <v>282</v>
-      </c>
       <c r="F136" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G136" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H136" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I136" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J136" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
@@ -6707,31 +6689,31 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C137" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D137" t="s">
+        <v>278</v>
+      </c>
+      <c r="E137" t="s">
         <v>280</v>
       </c>
-      <c r="E137" t="s">
-        <v>282</v>
-      </c>
       <c r="F137" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G137" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H137" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I137" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J137" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
@@ -6739,31 +6721,31 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C138" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D138" t="s">
+        <v>278</v>
+      </c>
+      <c r="E138" t="s">
         <v>280</v>
       </c>
-      <c r="E138" t="s">
-        <v>282</v>
-      </c>
       <c r="F138" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G138" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H138" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I138" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="J138" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -6771,31 +6753,31 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C139" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D139" t="s">
+        <v>278</v>
+      </c>
+      <c r="E139" t="s">
         <v>280</v>
       </c>
-      <c r="E139" t="s">
-        <v>282</v>
-      </c>
       <c r="F139" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G139" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H139" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I139" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="J139" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
@@ -6803,31 +6785,31 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C140" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D140" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E140" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F140" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G140" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H140" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I140" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="J140" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
@@ -6835,31 +6817,31 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C141" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D141" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E141" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F141" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G141" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H141" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I141" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J141" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
@@ -6867,31 +6849,31 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C142" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D142" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E142" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F142" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G142" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H142" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I142" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J142" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
@@ -6899,31 +6881,31 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C143" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D143" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E143" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F143" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G143" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H143" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I143" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J143" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
@@ -6931,31 +6913,31 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C144" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D144" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E144" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F144" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G144" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H144" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I144" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="J144" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.2">
@@ -6963,31 +6945,31 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C145" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D145" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E145" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F145" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G145" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H145" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I145" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J145" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
@@ -6995,31 +6977,31 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D146" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E146" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F146" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G146" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H146" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I146" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J146" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.2">
@@ -7027,31 +7009,31 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D147" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E147" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F147" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G147" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H147" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I147" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J147" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.2">
@@ -7059,31 +7041,31 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C148" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D148" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E148" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F148" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G148" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H148" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I148" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J148" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.2">
@@ -7091,31 +7073,31 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C149" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D149" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E149" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F149" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G149" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H149" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I149" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J149" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.2">
@@ -7123,31 +7105,31 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C150" t="s">
+        <v>277</v>
+      </c>
+      <c r="D150" t="s">
+        <v>278</v>
+      </c>
+      <c r="E150" t="s">
         <v>279</v>
       </c>
-      <c r="D150" t="s">
-        <v>280</v>
-      </c>
-      <c r="E150" t="s">
-        <v>283</v>
-      </c>
       <c r="F150" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G150" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H150" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I150" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="J150" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
@@ -7155,31 +7137,31 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C151" t="s">
+        <v>277</v>
+      </c>
+      <c r="D151" t="s">
+        <v>278</v>
+      </c>
+      <c r="E151" t="s">
         <v>279</v>
       </c>
-      <c r="D151" t="s">
-        <v>280</v>
-      </c>
-      <c r="E151" t="s">
-        <v>283</v>
-      </c>
       <c r="F151" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G151" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H151" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I151" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J151" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.2">
@@ -7187,31 +7169,31 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C152" t="s">
+        <v>277</v>
+      </c>
+      <c r="D152" t="s">
+        <v>278</v>
+      </c>
+      <c r="E152" t="s">
         <v>279</v>
       </c>
-      <c r="D152" t="s">
-        <v>280</v>
-      </c>
-      <c r="E152" t="s">
-        <v>281</v>
-      </c>
       <c r="F152" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G152" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H152" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I152" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="J152" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.2">
@@ -7219,31 +7201,31 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C153" t="s">
+        <v>277</v>
+      </c>
+      <c r="D153" t="s">
+        <v>278</v>
+      </c>
+      <c r="E153" t="s">
         <v>279</v>
       </c>
-      <c r="D153" t="s">
-        <v>280</v>
-      </c>
-      <c r="E153" t="s">
-        <v>281</v>
-      </c>
       <c r="F153" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G153" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H153" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I153" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="J153" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.2">
@@ -7251,31 +7233,31 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C154" t="s">
+        <v>277</v>
+      </c>
+      <c r="D154" t="s">
+        <v>278</v>
+      </c>
+      <c r="E154" t="s">
         <v>279</v>
       </c>
-      <c r="D154" t="s">
-        <v>280</v>
-      </c>
-      <c r="E154" t="s">
-        <v>281</v>
-      </c>
       <c r="F154" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G154" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H154" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I154" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J154" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.2">
@@ -7283,31 +7265,31 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C155" t="s">
+        <v>277</v>
+      </c>
+      <c r="D155" t="s">
+        <v>278</v>
+      </c>
+      <c r="E155" t="s">
         <v>279</v>
       </c>
-      <c r="D155" t="s">
-        <v>280</v>
-      </c>
-      <c r="E155" t="s">
-        <v>281</v>
-      </c>
       <c r="F155" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G155" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H155" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I155" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="J155" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.2">
@@ -7315,31 +7297,31 @@
         <v>163</v>
       </c>
       <c r="B156" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C156" t="s">
+        <v>277</v>
+      </c>
+      <c r="D156" t="s">
+        <v>278</v>
+      </c>
+      <c r="E156" t="s">
         <v>279</v>
       </c>
-      <c r="D156" t="s">
-        <v>280</v>
-      </c>
-      <c r="E156" t="s">
-        <v>281</v>
-      </c>
       <c r="F156" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G156" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H156" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I156" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="J156" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.2">
@@ -7347,31 +7329,31 @@
         <v>164</v>
       </c>
       <c r="B157" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C157" t="s">
+        <v>277</v>
+      </c>
+      <c r="D157" t="s">
+        <v>278</v>
+      </c>
+      <c r="E157" t="s">
         <v>279</v>
       </c>
-      <c r="D157" t="s">
-        <v>280</v>
-      </c>
-      <c r="E157" t="s">
-        <v>281</v>
-      </c>
       <c r="F157" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G157" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H157" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I157" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J157" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.2">
@@ -7379,31 +7361,31 @@
         <v>165</v>
       </c>
       <c r="B158" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C158" t="s">
+        <v>277</v>
+      </c>
+      <c r="D158" t="s">
+        <v>278</v>
+      </c>
+      <c r="E158" t="s">
         <v>279</v>
       </c>
-      <c r="D158" t="s">
-        <v>280</v>
-      </c>
-      <c r="E158" t="s">
-        <v>281</v>
-      </c>
       <c r="F158" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G158" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H158" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I158" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J158" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.2">
@@ -7411,31 +7393,31 @@
         <v>166</v>
       </c>
       <c r="B159" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C159" t="s">
+        <v>277</v>
+      </c>
+      <c r="D159" t="s">
+        <v>278</v>
+      </c>
+      <c r="E159" t="s">
         <v>279</v>
       </c>
-      <c r="D159" t="s">
-        <v>280</v>
-      </c>
-      <c r="E159" t="s">
-        <v>281</v>
-      </c>
       <c r="F159" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G159" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H159" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I159" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="J159" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.2">
@@ -7443,31 +7425,31 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C160" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D160" t="s">
+        <v>278</v>
+      </c>
+      <c r="E160" t="s">
         <v>280</v>
       </c>
-      <c r="E160" t="s">
-        <v>281</v>
-      </c>
       <c r="F160" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G160" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H160" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I160" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J160" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.2">
@@ -7475,31 +7457,31 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C161" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D161" t="s">
+        <v>278</v>
+      </c>
+      <c r="E161" t="s">
         <v>280</v>
       </c>
-      <c r="E161" t="s">
-        <v>281</v>
-      </c>
       <c r="F161" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G161" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H161" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I161" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J161" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.2">
@@ -7507,31 +7489,31 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C162" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D162" t="s">
+        <v>278</v>
+      </c>
+      <c r="E162" t="s">
         <v>280</v>
       </c>
-      <c r="E162" t="s">
-        <v>282</v>
-      </c>
       <c r="F162" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G162" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H162" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I162" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J162" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.2">
@@ -7539,31 +7521,31 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C163" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D163" t="s">
+        <v>278</v>
+      </c>
+      <c r="E163" t="s">
         <v>280</v>
       </c>
-      <c r="E163" t="s">
-        <v>282</v>
-      </c>
       <c r="F163" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G163" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H163" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I163" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J163" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.2">
@@ -7571,31 +7553,31 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C164" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D164" t="s">
+        <v>278</v>
+      </c>
+      <c r="E164" t="s">
         <v>280</v>
       </c>
-      <c r="E164" t="s">
-        <v>282</v>
-      </c>
       <c r="F164" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G164" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H164" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I164" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="J164" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.2">
@@ -7603,31 +7585,31 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C165" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D165" t="s">
+        <v>278</v>
+      </c>
+      <c r="E165" t="s">
         <v>280</v>
       </c>
-      <c r="E165" t="s">
-        <v>282</v>
-      </c>
       <c r="F165" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G165" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H165" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I165" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J165" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.2">
@@ -7635,31 +7617,31 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C166" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D166" t="s">
+        <v>278</v>
+      </c>
+      <c r="E166" t="s">
         <v>280</v>
       </c>
-      <c r="E166" t="s">
-        <v>282</v>
-      </c>
       <c r="F166" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G166" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H166" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I166" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J166" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.2">
@@ -7667,31 +7649,31 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C167" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D167" t="s">
+        <v>278</v>
+      </c>
+      <c r="E167" t="s">
         <v>280</v>
       </c>
-      <c r="E167" t="s">
-        <v>282</v>
-      </c>
       <c r="F167" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G167" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H167" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I167" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J167" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.2">
@@ -7699,31 +7681,31 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C168" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D168" t="s">
+        <v>278</v>
+      </c>
+      <c r="E168" t="s">
         <v>280</v>
       </c>
-      <c r="E168" t="s">
-        <v>282</v>
-      </c>
       <c r="F168" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G168" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H168" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I168" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J168" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.2">
@@ -7731,31 +7713,31 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C169" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D169" t="s">
+        <v>278</v>
+      </c>
+      <c r="E169" t="s">
         <v>280</v>
       </c>
-      <c r="E169" t="s">
-        <v>282</v>
-      </c>
       <c r="F169" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G169" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H169" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I169" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J169" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.2">
@@ -7763,31 +7745,31 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C170" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D170" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E170" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F170" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G170" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H170" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I170" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J170" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.2">
@@ -7795,31 +7777,31 @@
         <v>178</v>
       </c>
       <c r="B171" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C171" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D171" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E171" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F171" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G171" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H171" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I171" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J171" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.2">
@@ -7827,31 +7809,31 @@
         <v>179</v>
       </c>
       <c r="B172" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C172" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D172" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E172" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F172" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G172" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H172" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I172" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J172" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.2">
@@ -7859,31 +7841,31 @@
         <v>180</v>
       </c>
       <c r="B173" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C173" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D173" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E173" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F173" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G173" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H173" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I173" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="J173" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.2">
@@ -7891,31 +7873,31 @@
         <v>181</v>
       </c>
       <c r="B174" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C174" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D174" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E174" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F174" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G174" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H174" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I174" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J174" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.2">
@@ -7923,31 +7905,31 @@
         <v>182</v>
       </c>
       <c r="B175" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C175" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D175" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E175" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F175" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G175" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H175" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I175" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J175" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.2">
@@ -7955,31 +7937,31 @@
         <v>183</v>
       </c>
       <c r="B176" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C176" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D176" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E176" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F176" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G176" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H176" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I176" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J176" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.2">
@@ -7987,31 +7969,31 @@
         <v>184</v>
       </c>
       <c r="B177" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C177" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D177" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E177" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F177" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G177" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H177" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I177" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J177" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.2">
@@ -8019,31 +8001,31 @@
         <v>185</v>
       </c>
       <c r="B178" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C178" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D178" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E178" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F178" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G178" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H178" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I178" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="J178" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.2">
@@ -8051,95 +8033,31 @@
         <v>186</v>
       </c>
       <c r="B179" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C179" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D179" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E179" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F179" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G179" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H179" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I179" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="J179" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A180" t="s">
-        <v>187</v>
-      </c>
-      <c r="B180" t="s">
-        <v>278</v>
-      </c>
-      <c r="C180" t="s">
-        <v>279</v>
-      </c>
-      <c r="D180" t="s">
-        <v>280</v>
-      </c>
-      <c r="E180" t="s">
-        <v>283</v>
-      </c>
-      <c r="F180" t="s">
-        <v>284</v>
-      </c>
-      <c r="G180" t="s">
-        <v>290</v>
-      </c>
-      <c r="H180" t="s">
-        <v>291</v>
-      </c>
-      <c r="I180" t="s">
-        <v>471</v>
-      </c>
-      <c r="J180" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
-        <v>188</v>
-      </c>
-      <c r="B181" t="s">
-        <v>278</v>
-      </c>
-      <c r="C181" t="s">
-        <v>279</v>
-      </c>
-      <c r="D181" t="s">
-        <v>280</v>
-      </c>
-      <c r="E181" t="s">
-        <v>283</v>
-      </c>
-      <c r="F181" t="s">
-        <v>284</v>
-      </c>
-      <c r="G181" t="s">
-        <v>290</v>
-      </c>
-      <c r="H181" t="s">
-        <v>292</v>
-      </c>
-      <c r="I181" t="s">
-        <v>472</v>
-      </c>
-      <c r="J181" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
